--- a/Output/output.xlsx
+++ b/Output/output.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="600" firstSheet="0" activeTab="7" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-11700" yWindow="-21720" windowWidth="51840" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="7" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Readme" sheetId="1" state="visible" r:id="rId1"/>
@@ -975,7 +975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col width="20.7265625" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1045,7 +1045,7 @@
     <row r="2" ht="29" customHeight="1">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B2" s="12" t="inlineStr">
@@ -1055,12 +1055,12 @@
       </c>
       <c r="C2" s="12" t="inlineStr">
         <is>
-          <t>Lirilumab + Ipilimumab</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="D2" s="12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="E2" s="12" t="n">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>Randomized to Placebo TTS (adhesive patches)</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr"/>
@@ -1092,7 +1092,7 @@
     <row r="3" ht="31" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B3" s="12" t="inlineStr">
@@ -1102,12 +1102,12 @@
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>Lirilumab + Ipilimumab</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="D3" s="12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="E3" s="12" t="n">
@@ -1115,12 +1115,12 @@
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>Treatment</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Placebo TTS (adhesive patches)</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
@@ -1131,7 +1131,7 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>Treatment phase</t>
+          <t>Treatment One</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr"/>
@@ -1139,7 +1139,7 @@
     <row r="4" ht="15.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B4" s="12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>Lirilumab + Ipilimumab</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="E4" s="12" t="n">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>Follow-up</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Placebo TTS (adhesive patches)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1175,104 +1175,584 @@
           <t xml:space="preserve"> </t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>not willing to do online questionnaire: transition to StudyEpoch_4</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Follow-up phase</t>
+          <t>Treatment Two</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
     </row>
     <row r="5" ht="31" customHeight="1">
-      <c r="A5" s="12" t="inlineStr"/>
-      <c r="B5" s="12" t="inlineStr"/>
-      <c r="C5" s="12" t="inlineStr"/>
-      <c r="D5" s="12" t="inlineStr"/>
-      <c r="E5" s="12" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="inlineStr">
+        <is>
+          <t>Placebo</t>
+        </is>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>Placebo</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>Placebo TTS (adhesive patches)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Treatment Three</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
     </row>
     <row r="6" ht="43.5" customHeight="1">
-      <c r="A6" s="12" t="inlineStr"/>
-      <c r="B6" s="12" t="inlineStr"/>
-      <c r="C6" s="12" t="inlineStr"/>
-      <c r="D6" s="12" t="inlineStr"/>
-      <c r="E6" s="12" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>Placebo</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>Follow up</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Follow Up Element</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
     </row>
     <row r="7" ht="118" customHeight="1">
-      <c r="A7" s="12" t="inlineStr"/>
-      <c r="B7" s="12" t="inlineStr"/>
-      <c r="C7" s="12" t="inlineStr"/>
-      <c r="D7" s="12" t="inlineStr"/>
-      <c r="E7" s="12" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
-      <c r="G7" s="8" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>Xanomeline Low Dose</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>Screening</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
+        <is>
+          <t>Screening Element</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Randomized to Xanomeline TTS (adhesive patches) 50 cm2, 54 mg</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Screening</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
     </row>
     <row r="8" ht="31" customHeight="1">
-      <c r="A8" s="12" t="inlineStr"/>
-      <c r="B8" s="12" t="inlineStr"/>
-      <c r="C8" s="12" t="inlineStr"/>
-      <c r="D8" s="12" t="inlineStr"/>
-      <c r="E8" s="12" t="inlineStr"/>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="5" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="inlineStr">
+        <is>
+          <t>Xanomeline Low Dose</t>
+        </is>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>Xanomeline TTS (adhesive patches) 50 cm2, 54 mg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Treatment One</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
     </row>
     <row r="9" ht="15.5" customHeight="1">
-      <c r="A9" s="12" t="inlineStr"/>
-      <c r="B9" s="12" t="inlineStr"/>
-      <c r="C9" s="12" t="inlineStr"/>
-      <c r="D9" s="12" t="inlineStr"/>
-      <c r="E9" s="12" t="inlineStr"/>
-      <c r="F9" s="10" t="inlineStr"/>
-      <c r="G9" s="8" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="inlineStr">
+        <is>
+          <t>Xanomeline Low Dose</t>
+        </is>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>Xanomeline TTS (adhesive patches) 50 cm2, 54 mg</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>not willing to do online questionnaire: transition to StudyEpoch_4</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Treatment Two</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
     </row>
     <row r="10" ht="72.5" customHeight="1">
-      <c r="A10" s="12" t="inlineStr"/>
-      <c r="B10" s="12" t="inlineStr"/>
-      <c r="C10" s="12" t="inlineStr"/>
-      <c r="D10" s="12" t="inlineStr"/>
-      <c r="E10" s="12" t="inlineStr"/>
-      <c r="F10" s="8" t="inlineStr"/>
-      <c r="G10" s="8" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="inlineStr">
+        <is>
+          <t>Xanomeline Low Dose</t>
+        </is>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>Xanomeline TTS (adhesive patches) 50 cm2, 54 mg</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Treatment Three</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
     </row>
     <row r="11" ht="137.5" customHeight="1">
-      <c r="A11" s="12" t="inlineStr"/>
-      <c r="B11" s="12" t="inlineStr"/>
-      <c r="C11" s="12" t="inlineStr"/>
-      <c r="D11" s="12" t="inlineStr"/>
-      <c r="E11" s="12" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
-      <c r="G11" s="8" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Xanomeline Low Dose</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Follow up</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Follow Up Element</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Xanomeline High Dose</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Screening</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Screening Element</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Randomized to Xanomeline TTS (adhesive patches) 50 cm2, 54 mg Xanomeline TTS (adhesive patches) 50 cm2, 54 mg + 25 cm2, 27 mg Xanomeline TTS (adhesive patches) 50 cm2, 54 mg</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Screening</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Xanomeline High Dose</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>High - Start</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Xanomeline TTS (adhesive patches) 50 cm2, 54 mg</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Treatment One</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Xanomeline High Dose</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>High - Middle</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Xanomeline TTS (adhesive patches) 50 cm2, 54 mg + 25 cm2, 27 mg</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>not willing to do online questionnaire: transition to StudyEpoch_4</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Treatment Two</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Xanomeline High Dose</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>High - End</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Xanomeline TTS (adhesive patches) 50 cm2, 54 mg</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Treatment Three</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Xanomeline High Dose</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Follow up</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Follow Up Element</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Follow Up</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1342,7 +1822,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
@@ -1367,7 +1847,7 @@
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
-          <t>Start treatment</t>
+          <t>Completion of all screening activities and no more than 2 weeks from informed consent</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
@@ -1383,7 +1863,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
@@ -1393,24 +1873,20 @@
       </c>
       <c r="C3" s="9" t="inlineStr">
         <is>
-          <t>Treatment</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>None,</t>
+          <t>Placebo TTS (adhesive patches)</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>Start treatment</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>End treatment</t>
-        </is>
-      </c>
+          <t>Administration\xa0of\xa0first\xa0dose</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="n"/>
       <c r="G3" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
@@ -1424,7 +1900,7 @@
     <row r="4" ht="29" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
@@ -1434,22 +1910,22 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>Follow-up</t>
+          <t>Follow up</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Follow Up Element</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>End treatment</t>
+          <t>End\xa0of\xa0last\xa0scheduled\xa0visit\xa0on\xa0study\xa0(including\xa0early\xa0termination)</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>End follow-up activities</t>
+          <t>Completion\xa0of\xa0all\xa0specified\xa0followup\xa0activities\xa0(which\xa0vary\xa0on\xa0a\xa0patient-by-patient\xa0basis)</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -1462,52 +1938,161 @@
       <c r="J4" t="inlineStr"/>
     </row>
     <row r="5" ht="29" customHeight="1">
-      <c r="A5" s="9" t="inlineStr"/>
-      <c r="B5" s="9" t="inlineStr"/>
-      <c r="C5" s="9" t="inlineStr"/>
-      <c r="D5" s="9" t="inlineStr"/>
-      <c r="E5" s="9" t="inlineStr"/>
-      <c r="F5" s="13" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>Xanomeline TTS (adhesive patches) 50 cm2, 54 mg</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>Administration\xa0of\xa0first\xa0dose</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="inlineStr">
+        <is>
+          <t>Element Description</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
     </row>
     <row r="6" ht="29" customHeight="1">
-      <c r="A6" s="9" t="inlineStr"/>
-      <c r="B6" s="9" t="inlineStr"/>
-      <c r="C6" s="9" t="inlineStr"/>
-      <c r="D6" s="9" t="inlineStr"/>
-      <c r="E6" s="9" t="inlineStr"/>
-      <c r="F6" s="13" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>High - Start</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>Xanomeline TTS (adhesive patches) 50 cm2, 54 mg</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>Randomized</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
+        <is>
+          <t>Element Start Rule</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
     </row>
     <row r="7" ht="29" customHeight="1">
-      <c r="A7" s="9" t="inlineStr"/>
-      <c r="B7" s="9" t="inlineStr"/>
-      <c r="C7" s="9" t="inlineStr"/>
-      <c r="D7" s="9" t="inlineStr"/>
-      <c r="E7" s="9" t="inlineStr"/>
-      <c r="F7" s="13" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr"/>
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>High - Middle</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>Xanomeline TTS (adhesive patches) 50 cm2, 54 mg + 25 cm2, 27 mg</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="inlineStr">
+        <is>
+          <t>Administration\xa0of\xa0first\xa0dose\xa0(from\xa0patches\xa0supplied\xa0at\xa0Visit\xa04)</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="inlineStr">
+        <is>
+          <t>Element End Rule</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
     </row>
     <row r="8" ht="29" customHeight="1">
-      <c r="A8" s="9" t="inlineStr"/>
-      <c r="B8" s="9" t="inlineStr"/>
-      <c r="C8" s="9" t="inlineStr"/>
-      <c r="D8" s="9" t="inlineStr"/>
-      <c r="E8" s="9" t="inlineStr"/>
-      <c r="F8" s="13" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>High - End</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>Xanomeline TTS (adhesive patches) 50 cm2, 54 mg</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="inlineStr">
+        <is>
+          <t>Administration\xa0of\xa0first\xa0dose\xa0(from\xa0patches\xa0supplied\xa0at\xa0Visit\xa012)</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
+        <is>
+          <t>Element Duration</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1520,7 +2105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.6328125" customWidth="1" min="1" max="2"/>
@@ -1583,7 +2168,7 @@
     <row r="2" ht="43.5" customHeight="1">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
@@ -1596,18 +2181,18 @@
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>Screening</t>
+          <t>Screening 1</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr"/>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>Lirilumab + Ipilimumab</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="H2" s="8" t="inlineStr">
@@ -1617,14 +2202,14 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Signed informed consent</t>
+          <t>Subject identifier</t>
         </is>
       </c>
     </row>
     <row r="3" ht="29" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
@@ -1637,7 +2222,7 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>Day 1</t>
+          <t>Screening 2</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
@@ -1647,29 +2232,29 @@
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>Lirilumab + Ipilimumab</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>Not defined</t>
+          <t>subject leaves clinic after connection of ambulatory ECG machine</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Not defined</t>
+          <t>subject has connection of ambulatory ECG machine removed</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
@@ -1682,7 +2267,7 @@
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>Week 2</t>
+          <t>Baseline</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
@@ -1692,29 +2277,29 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>Lirilumab + Ipilimumab</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>Not defined</t>
+          <t>Radomized</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Not defined</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="5" ht="29" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
@@ -1727,7 +2312,7 @@
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>Week 3</t>
+          <t>Week 2</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -1737,29 +2322,29 @@
       </c>
       <c r="F5" s="8" t="inlineStr">
         <is>
-          <t>Lirilumab + Ipilimumab</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>Not defined</t>
+          <t>End of treatment</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Not defined</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="6" ht="29" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B6" s="8" t="inlineStr">
@@ -1782,29 +2367,29 @@
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Lirilumab + Ipilimumab</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>Not defined</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Not defined</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="7" ht="29" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B7" s="8" t="inlineStr">
@@ -1817,7 +2402,7 @@
       </c>
       <c r="D7" s="8" t="inlineStr">
         <is>
-          <t>Week 10</t>
+          <t>Week 6</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -1827,29 +2412,29 @@
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Lirilumab + Ipilimumab</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>Not defined</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Not defined</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="8" ht="29" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B8" s="8" t="inlineStr">
@@ -1862,7 +2447,7 @@
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>Week 11</t>
+          <t>Week 8</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
@@ -1872,29 +2457,29 @@
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Lirilumab + Ipilimumab</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="H8" s="8" t="inlineStr">
         <is>
-          <t>Not defined</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Not defined</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="9" ht="29" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
@@ -1907,7 +2492,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Week 13</t>
+          <t>Week 12</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -1917,29 +2502,29 @@
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>Lirilumab + Ipilimumab</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Not defined</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Not defined</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="10" ht="29" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B10" s="8" t="inlineStr">
@@ -1952,7 +2537,7 @@
       </c>
       <c r="D10" s="8" t="inlineStr">
         <is>
-          <t>Week 24</t>
+          <t>Week 16</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -1962,29 +2547,29 @@
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>Lirilumab + Ipilimumab</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>Not defined</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Not defined</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1997,7 +2582,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Week 36</t>
+          <t>Week 20</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2007,29 +2592,29 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lirilumab + Ipilimumab</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Not defined</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Not defined</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2042,7 +2627,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Week 48</t>
+          <t>Week 24</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2052,29 +2637,29 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lirilumab + Ipilimumab</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Not defined</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Not defined</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2087,7 +2672,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Week 60</t>
+          <t>Week 26</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2097,29 +2682,29 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lirilumab + Ipilimumab</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Placebo</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Not defined</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Not defined</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2128,43 +2713,39 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Follow-up 1</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
-      </c>
+          <t>Screening 1</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lirilumab + Ipilimumab</t>
+          <t>ACTLOW</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Xanomeline Low Dose</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Not defined</t>
+          <t>completion of screening activities</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Not defined</t>
+          <t>Subject identifier</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2173,11 +2754,11 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Follow-up 2</t>
+          <t>Screening 2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2187,22 +2768,1008 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lirilumab + Ipilimumab</t>
+          <t>ACTLOW</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Xanomeline Low Dose</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Not defined</t>
+          <t>subject leaves clinic after connection of ambulatory ECG machine</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Not defined</t>
+          <t>subject has connection of ambulatory ECG machine removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Xanomeline Low Dose</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Radomized</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>4</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Xanomeline Low Dose</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>End of treatment</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Xanomeline Low Dose</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Xanomeline Low Dose</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>7</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Week 8</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Xanomeline Low Dose</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>8</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Week 12</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Xanomeline Low Dose</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>9</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Week 16</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Xanomeline Low Dose</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Week 20</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Xanomeline Low Dose</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>11</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Week 24</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Xanomeline Low Dose</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>12</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Week 26</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ACTLOW</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Xanomeline Low Dose</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Screening 1</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Xanomeline High Dose</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>completion of screening activities</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Subject identifier</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Screening 2</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Xanomeline High Dose</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>subject leaves clinic after connection of ambulatory ECG machine</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>subject has connection of ambulatory ECG machine removed</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Xanomeline High Dose</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Radomized</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Week 2</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Xanomeline High Dose</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>End of treatment</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Week 4</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Xanomeline High Dose</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>6</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Week 6</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Xanomeline High Dose</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>7</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Week 8</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Xanomeline High Dose</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>8</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Week 12</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Xanomeline High Dose</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>9</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Week 16</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Xanomeline High Dose</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>10</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Week 20</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Xanomeline High Dose</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>11</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Week 24</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Xanomeline High Dose</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>TV</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>12</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Week 26</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>ACTHIGH</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Xanomeline High Dose</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -2220,7 +3787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.81640625" defaultRowHeight="14.5"/>
   <cols>
     <col width="18.6328125" customWidth="1" min="1" max="2"/>
@@ -2321,7 +3888,7 @@
     <row r="2" ht="29" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
@@ -2336,7 +3903,7 @@
       </c>
       <c r="D2" s="9" t="inlineStr">
         <is>
-          <t>Histologic confirmation of one of the following solid tumors that is advanced (unresectable or metastatic) for dose escalation or cohort expansion:Non-Small Cell Lung Cancer (NSCLC), Castrate</t>
+          <t>Males and postmenopausal females at least 50.0 years of age.</t>
         </is>
       </c>
       <c r="E2" s="9" t="inlineStr">
@@ -2357,18 +3924,13 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> Resistant Prostate Cancer (CRPC), Melanoma (MEL)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="29" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
@@ -2383,7 +3945,7 @@
       </c>
       <c r="D3" s="9" t="inlineStr">
         <is>
-          <t>At least one measurable lesion at baseline by Computed tomography (CT) or Magnetic resonance imaging (MRI) as per Response Evaluation Criteria in Solid Tumors (RECIST) 1.1 criteria</t>
+          <t>Patients with Probable Mild to Moderate Alzheimer's Disease as defined by National Institute of Neurological and Communicative Disorders and Stroke (NINCDS) and the Alzheimer\'s Disease and Related</t>
         </is>
       </c>
       <c r="E3" s="9" t="inlineStr">
@@ -2404,13 +3966,18 @@
       <c r="H3" s="9" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Disorders Association (ADRDA) guidelines (Attachment LZZT.7).</t>
         </is>
       </c>
     </row>
     <row r="4" ht="29" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
@@ -2425,7 +3992,7 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>Biopsies: Subjects in the melanoma cohort must have at least 1 tumor site that can be biopsied at acceptable clinical risk</t>
+          <t>MMSE score of 10 to 23.</t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
@@ -2452,7 +4019,7 @@
     <row r="5" ht="43.5" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -2467,7 +4034,7 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>Eastern Cooperative Oncology Group (ECOG) status of 0 or 1</t>
+          <t>Hachinski Ischemic Scale score of &lt;=4 (Attachment LZZT.8).</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
@@ -2494,7 +4061,7 @@
     <row r="6" ht="29" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -2509,7 +4076,7 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Estimated life expectancy of &gt;= 12 weeks</t>
+          <t>CNS imaging (CT scan or MRI of brain) compatible with AD within past 1 year.</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
@@ -2536,7 +4103,7 @@
     <row r="7" ht="29" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -2551,7 +4118,7 @@
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>White blood cell (WBC) &gt;=2000/microL, Neutrophils &gt;=1500/microL, Platelets &gt;= 100x1000/microL, Hemoglobin &gt;= 8.5 g/dL, Creatinine Clearance &lt;= 1.5 X upper limit of normal (ULN) mL/min, Alanine</t>
+          <t>Investigator has obtained informed consent signed by the patient (and/or legal representative) and by the caregiver.</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
@@ -2572,18 +4139,13 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> aminotransferase (ALT) and Aspartate aminotransferase (AST) &lt;= 3x ULN</t>
         </is>
       </c>
     </row>
     <row r="8" ht="29" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -2598,7 +4160,7 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Normal Thyroid function or be on stable hormone supplementation</t>
+          <t>"Geographic proximity to investigator's site that allows adequate follow-up.",</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
@@ -2625,7 +4187,7 @@
     <row r="9" ht="43.5" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -2640,12 +4202,12 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Participation in any prior clinical study with BMS-936558 or ipilimumab that has overall survival listed as a primary/co-primary endpoint</t>
+          <t>A reliable caregiver who is in frequent or daily contact with the patient and who will accompany the patient to the office and/or be available by telephone at designated times, will monitor</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>EXCLUSION</t>
+          <t>INCLUSION</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
@@ -2661,13 +4223,23 @@
       <c r="H9" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> administration of prescribed medications, and will be responsible for the overall care of the patient at home. The caregiver and the patient must be able to communicate in English and willing to</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> comply with 26 weeks of transdermal therapy.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2682,7 +4254,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Subjects with known or suspected brain metastasis</t>
+          <t>Persons who have previously completed or withdrawn from this study or any other study investigating xanomeline TTS or the oral formulation of xanomeline.</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2709,7 +4281,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2724,7 +4296,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Subjects with active autoimmune disease, uncontrolled or significant cardiovascular disease</t>
+          <t>"Use of any investigational agent or approved Alzheimer's therapeutic medication within 30 days prior to enrollment into the study.",</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2751,7 +4323,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2766,7 +4338,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Prior therapy with anti- Cytotoxic T-Lymphocyte Antigen 4 (CTLA4) antibody or anti- Killer cell immunoglobulin-like receptor (KIR) antibody</t>
+          <t>Serious illness which required hospitalization within 3 months of screening.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2793,7 +4365,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2808,7 +4380,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Grade 2 neuropathy</t>
+          <t>Diagnosis of serious neurological conditions, including - Stroke or vascular dementia documented by clinical history and/or radiographic findings interpretable by the investigator as indicative of</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2827,6 +4399,894 @@
         </is>
       </c>
       <c r="H13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> these disorders; - Seizure disorder other than simple childhood febrile seizures; - Severe head trauma resulting in protracted loss of consciousness within the last 5 years, or multiple episodes of</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> head trauma; - Parkinson\'s disease; - Multiple sclerosis; - Amyotrophic lateral sclerosis; - Myasthenia gravis.;</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Episode of depression meeting DSM-IV criteria within 3 months of screening.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>EXCLUSION</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>A history within the last 5 years of the following: - Schizophrenia; - Bipolar Disease; - Ethanol or psychoactive drug abuse or dependence. ;</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>EXCLUSION</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>A history of syncope within the last 5 years.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>EXCLUSION</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>16b</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Evidence from ECG recording at screening of any of the following conditions : - Left bundle branch block; - Bradycardia &lt;=50 beats per minute; - Sinus pauses &gt;2 seconds; - Second or third degree heart</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>EXCLUSION</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> block unless treated with a pacemaker; - Wolff-Parkinson-White syndrome; - Sustained supraventricular tachyarrhythmia including SVT≥10 sec, atrial fibrillation, atrial flutter.; - Ventricular</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> tachycardia at a rate of ≥120 beats per minute lasting≥10 seconds.;</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>A history within the last 5 years of a serious cardiovascular disorder, including - Clinically significant arrhythmia; - Symptomatic sick sinus syndrome not treated with a pacemaker; - Congestive</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>EXCLUSION</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> heart failure refractory to treatment; - Angina except angina controlled with PRN nitroglycerin; - Resting heart rate &lt;50 or &gt;100 beats per minute, on physical exam; - Uncontrolled hypertension.;</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>A history within the last 5 years of a serious gastrointestinal disorder, including - Chronic peptic/duodenal/gastric/esophageal ulcer that are untreated or refractory to treatment; - Symptomatic</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>EXCLUSION</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> diverticular disease; - Inflammatory bowel disease; - Pancreatitis; - Hepatitis; - Cirrhosis of the liver.;</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>A history within the last 5 years of a serious endocrine disorder, including - Uncontrolled Insulin Dependent Diabetes Mellitus (IDDM); - Diabetic ketoacidosis; - Untreated hyperthyroidism; -</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>EXCLUSION</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Untreated hypothyroidism; - Other untreated endocrinological disorder;</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>A history within the last 5 years of a serious respiratory disorder, including - Asthma with bronchospasm refractory to treatment; - Decompensated chronic obstructive pulmonary disease.;</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>EXCLUSION</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>A history within the last 5 years of a serious genitourinary disorder, including - Renal failure; - Uncontrolled urinary retention.;</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>EXCLUSION</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>A history within the last 5 years of a serious rheumatologic disorder, including - Lupus; - Temporal arteritis; - Severe rheumatoid arthritis.;</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>EXCLUSION</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>A known history of human immunodeficiency virus (HIV) within the last 5 years.</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>EXCLUSION</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>A history within the last 5 years of a serious infectious disease including - a) Neurosyphilis; - b) Meningitis; - c) Encephalitis.;</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>EXCLUSION</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>A history within the last 5 years of a primary or recurrent malignant disease with the exception of resected cutaneous squamous cell carcinoma in situ, basal cell carcinoma, cervical carcinoma in</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>EXCLUSION</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> situ, or in situ prostate cancer with a normal PSA postresection.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Visual, hearing, or communication disabilities impairing the ability to participate in the study; (for example, inability to speak or understand English, illiteracy).</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>EXCLUSION</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>27b</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>"Laboratory test values exceeding the Lilly Reference Range III for the patient's age in any of the following analytes: ↑ creatinine, ↑ total bilirubin, ↑ SGOT, ↑ SGPT, ↑ alkaline phosphatase, ↑ GGT,</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>EXCLUSION</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ↑↓ hemoglobin, ↑↓ white blood cell count, ↑↓ platelet count, ↑↓ serum sodium, potassium, or calcium.If values exceed these laboratory reference ranges, clinical significance will be judged by the</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> monitoring physicians. If the monitoring physician determines that the deviation from the reference range is not clinically significant, the patient may be included in the study. This decision will</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> be documented.",</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>28b</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Central laboratory test values below reference range for folate, and Vitamin B 12 , and outside reference range for thyroid function tests. - Folate reference range 2.0 to 25.0 ng/mL. Patients will be</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>EXCLUSION</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> allowed to enroll if their folate levels are above the upper end of the range if patients are taking vitamin supplements. ; - Vitamin B 12 reference range 130 to 900 pg/mL. Patients will be allowed</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> to enroll if their B 12 levels are above the upper reference range if patients are taking oral vitamin supplements. ; - Thyroid functions Thyroid Uptake reference range 25 to 38%. Patients will be</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> allowed to enroll with results of 23 to 51% provided the remainder of the thyroid profile is normal and there are no clinical signs or symptoms of thyroid abnormality. ; - TSH reference range 0.32 to</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> 5.0. Patients will be allowed to enroll with results of 0.03 to 6.2 if patients are taking stable doses of exogenous thyroid supplements, with normal free thyroid index, and show no clinical signs or</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> symptoms of thyroid abnormality. ; - Total T4 reference range 4.5 to 12.5. Patients will be allowed to enroll with results of 4.1 to 13.4 if patients are taking stable doses of exogenous thyroid</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> hormone, with normal free thyroid index, and show no clinical signs or symptoms of thyroid abnormality. ; - Free Thyroid Index reference range 1.1 to 4.6. ;</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>29b</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Positive syphilis screening.Positive syphilis screening. As determined by positive RPR followed up by confirmatory FTA-Abs. Confirmed patients are excluded unless there is a documented medical history</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>EXCLUSION</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> of an alternative disease (for example, yaws) which caused the lab abnormality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>30b</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Glycosylated hemoglobin (A1C). Required only on patients with known diabetes mellitus or random blood sugar &gt;200 on screening labs. Patients will be excluded if levels are &gt;9.5%</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>EXCLUSION</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>TI</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>31b</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Treatment with the following medications within the specified washout periods prior to enrollment and during the study:</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>EXCLUSION</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -2844,7 +5304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:P52"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col width="19.7265625" bestFit="1" customWidth="1" style="1" min="1" max="1"/>
@@ -2923,7 +5383,7 @@
     <row r="2" ht="58" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B2" s="9" t="inlineStr">
@@ -2943,17 +5403,17 @@
       </c>
       <c r="E2" s="9" t="inlineStr">
         <is>
-          <t>AGEMIN</t>
+          <t>ADAPT</t>
         </is>
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>Planned Minimum Age of Subjects</t>
+          <t>Adaptive Design</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
         <is>
-          <t>P18Y</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -2965,7 +5425,7 @@
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B3" s="9" t="inlineStr">
@@ -2985,7 +5445,7 @@
       </c>
       <c r="E3" s="9" t="inlineStr">
         <is>
-          <t>AGEMAX</t>
+          <t>AGEMIN</t>
         </is>
       </c>
       <c r="F3" s="10" t="inlineStr">
@@ -2995,7 +5455,7 @@
       </c>
       <c r="G3" s="10" t="inlineStr">
         <is>
-          <t>P120Y</t>
+          <t>P50Y</t>
         </is>
       </c>
       <c r="H3" s="9" t="inlineStr">
@@ -3007,7 +5467,7 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
@@ -3015,27 +5475,29 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="C4" s="9" t="n">
-        <v>1</v>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>LIR</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>CRMDUR</t>
+          <t>AGEMAX</t>
         </is>
       </c>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>Confirmed Response Minimum Duration</t>
+          <t>Planned Minimum Age of Subjects</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>P100Y</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -3047,7 +5509,7 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -3056,26 +5518,26 @@
         </is>
       </c>
       <c r="C5" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>IPI</t>
+          <t>INV01</t>
         </is>
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>CRMDUR</t>
+          <t>CONNAME</t>
         </is>
       </c>
       <c r="F5" s="13" t="inlineStr">
         <is>
-          <t>Confirmed Response Minimum Duration</t>
+          <t>Contact Name</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Mr. X</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -3087,7 +5549,7 @@
     <row r="6" ht="43.5" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -3100,22 +5562,22 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>Indication_1</t>
+          <t>INV01</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>INDIC</t>
+          <t>CONROLE</t>
         </is>
       </c>
       <c r="F6" s="13" t="inlineStr">
         <is>
-          <t>Trial Disease/Condition Indication; Trial Disease/Condition Indication Description</t>
+          <t>Contact Role</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Non-Small Cell Lung Cancer (NSCLC)</t>
+          <t>Investigator</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -3127,7 +5589,7 @@
     <row r="7" ht="29" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -3136,26 +5598,26 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="9" t="inlineStr">
         <is>
-          <t>Indication_2</t>
+          <t>XINONILINE50</t>
         </is>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>INDIC</t>
+          <t>CRMDUR</t>
         </is>
       </c>
       <c r="F7" s="13" t="inlineStr">
         <is>
-          <t>Trial Disease/Condition Indication; Trial Disease/Condition Indication Description</t>
+          <t>Confirmed Response Minimum Duration</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>Castrate Resistant Prostate Cancer (CRPC)</t>
+          <t>P1D</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -3167,7 +5629,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -3176,26 +5638,26 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Indication_3</t>
+          <t>XINONILINE25</t>
         </is>
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>INDIC</t>
+          <t>CRMDUR</t>
         </is>
       </c>
       <c r="F8" s="13" t="inlineStr">
         <is>
-          <t>Trial Disease/Condition Indication; Trial Disease/Condition Indication Description</t>
+          <t>Confirmed Response Minimum Duration</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>Melanoma (MEL)</t>
+          <t>P1D</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3207,7 +5669,7 @@
     <row r="9" ht="29" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -3215,56 +5677,39 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
+      <c r="C9" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>PLACEBO</t>
         </is>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>INTMODEL</t>
+          <t>CRMDUR</t>
         </is>
       </c>
       <c r="F9" s="13" t="inlineStr">
         <is>
-          <t>Intervention Model</t>
+          <t>Confirmed Response Minimum Duration</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
         <is>
-          <t>SINGLE GROUP</t>
+          <t>P1D</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>C82640</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>//www.cdisc.org</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
         </is>
       </c>
     </row>
     <row r="10" ht="29" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -3277,49 +5722,34 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>LIR</t>
+          <t>XINONILINE50</t>
         </is>
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>INTTYPE</t>
+          <t>DOSE</t>
         </is>
       </c>
       <c r="F10" s="13" t="inlineStr">
         <is>
-          <t>Intervention Type</t>
+          <t>Dose Level; Dose per Administration</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>DRUG</t>
+          <t>54.0, 81.0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>C1909</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>http://www.cdisc.org</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
         </is>
       </c>
     </row>
     <row r="11" ht="29" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -3328,26 +5758,26 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>IPI</t>
+          <t>XINONILINE50</t>
         </is>
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>INTTYPE</t>
+          <t>DOSFRQ</t>
         </is>
       </c>
       <c r="F11" s="13" t="inlineStr">
         <is>
-          <t>Intervention Type</t>
+          <t>Dosing Frequency</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>DRUG</t>
+          <t>QD</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3357,7 +5787,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>C1909</t>
+          <t>C25473</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -3374,7 +5804,7 @@
     <row r="12" ht="43.5" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -3382,41 +5812,54 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
+      <c r="C12" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>XINONILINE50</t>
         </is>
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>NARMS</t>
+          <t>DOSFRQ</t>
         </is>
       </c>
       <c r="F12" s="13" t="inlineStr">
         <is>
-          <t>Planned Number of Arms</t>
+          <t>Dosing Frequency</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>QD</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>C25473</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>//www.cdisc.org</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3424,41 +5867,54 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
+      <c r="C13" t="n">
+        <v>1</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>XINONILINE50</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>NCOHORT</t>
+          <t>DOSU</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Number of Groups/Cohorts</t>
+          <t>Dose Units</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Milligram</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>C28253</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>http://www.cdisc.org</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3467,38 +5923,53 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>OBJ1</t>
+          <t>XINONILINE50</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OBJPRIM</t>
+          <t>DOSU</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Study Primary Objective; Trial Primary Objective</t>
+          <t>Dose Units</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Primary objective texts not available from ClinicalTrials.gov.&lt;/p&gt;</t>
+          <t>Milligram</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>C28253</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>//www.cdisc.org</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3506,27 +5977,29 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="C15" t="n">
-        <v>1</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>OBJ2</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OBJSEC</t>
+          <t>EXTTIND</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Study Secondary Objective; Trial Secondary Objective</t>
+          <t>Extension Trial Indicator</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Secondary objective texts not available from ClinicalTrials.gov.&lt;/p&gt;</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -3538,7 +6011,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3546,27 +6019,29 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="C16" t="n">
-        <v>1</v>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>OBJ1</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OUTMSPRI</t>
+          <t>HLTSUBJI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Primary Outcome Measure</t>
+          <t>Healthy Subject Indicator</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Safety as measured by the rate of adverse events, and serious adverse events [Time Frame: Approximately 510 days</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -3578,7 +6053,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3591,22 +6066,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>OBJ2</t>
+          <t>Indication_1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>OUTMSSEC</t>
+          <t>INDIC</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Secondary Outcome Measure</t>
+          <t>Trial Disease/Condition Indication; Trial Disease/Condition Indication Description</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Efficacy as measured by tumor assessment [Time Frame: Assessed from the start of treatment (ay 1) to the end of treatment (week 60) and for 90 days in follow-up</t>
+          <t>"Alzheimer's disease",</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3618,7 +6093,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3626,29 +6101,27 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
+      <c r="C18" t="n">
+        <v>2</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>Indication_2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>PLANSUB</t>
+          <t>INDIC</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Anticipated Enrollment; Planned Enrollment; Planned Number of Subjects; Target Enrollment</t>
+          <t>Trial Disease/Condition Indication; Trial Disease/Condition Indication Description</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>"Alzheimer's disease"</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3660,7 +6133,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3680,29 +6153,44 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>SEXPOP</t>
+          <t>INTMODEL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sex of Participants</t>
+          <t>Intervention Model</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>['Female', 'Male']</t>
+          <t>Parallel Study</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>C82639</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>//www.cdisc.org</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3710,41 +6198,54 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
+      <c r="C20" t="n">
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>XINONILINE50</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>SPONSOR</t>
+          <t>INTTYPE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Clinical Study Sponsor; Sponsor; Study Sponsor</t>
+          <t>Intervention Type</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb</t>
+          <t>DRUG</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>C1909</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>http://www.cdisc.org</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3752,29 +6253,27 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
+      <c r="C21" t="n">
+        <v>2</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>XINONILINE25</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>STYPE</t>
+          <t>INTTYPE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Study Type; Study Type Classification</t>
+          <t>Intervention Type</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Interventional Study</t>
+          <t>DRUG</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3784,12 +6283,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>C98388</t>
+          <t>C1909</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>//www.cdisc.org</t>
+          <t>http://www.cdisc.org</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -3801,7 +6300,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3809,29 +6308,27 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
+      <c r="C22" t="n">
+        <v>3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>PLACEBO</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>TBLIND</t>
+          <t>INTTYPE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Study Blinding Design; Study Blinding Schema; Study Masking Design; Trial Blinding Design; Trial Blinding Schema; Trial Masking Design</t>
+          <t>Intervention Type</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>OPEN LABEL</t>
+          <t>DRUG</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3841,12 +6338,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>C49659</t>
+          <t>C1909</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>//www.cdisc.org</t>
+          <t>http://www.cdisc.org</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -3858,7 +6355,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3878,44 +6375,29 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>THERAREA</t>
+          <t>NARMS</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Therapeutic Area</t>
+          <t>Planned Number of Arms</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Oncology</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>LP32910-9</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>LOINC</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3923,54 +6405,41 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>1</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Code_152</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>TINDTP</t>
+          <t>NCOHORT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trial Intent Type</t>
+          <t>Number of Groups/Cohorts</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Treatment Study</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>C49656</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>http://www.cdisc.org</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>2025-09-26</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3978,29 +6447,27 @@
           <t>TS</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
-        </is>
+      <c r="C25" t="n">
+        <v>1</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>OBJ1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>TITLE</t>
+          <t>OBJPRIM</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Official Study Title; Study Title; Trial Title</t>
+          <t>Study Primary Objective; Trial Primary Objective</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>A Phase 1 Study of BMS-986015, an Anti-KIR Monoclonal Antibody, Administered With Ipilimumab, an Anti-CTLA4 Monoclonal Antibody, in Subjects With Select Advanced Solid Tumors</t>
+          <t>To determine if there is a statistically significant relationship (overall Type 1 erroralpha=0.05) between the change in both the ADAS-Cog (11) and CIBIC+ scores, and drug dose (0, 50 cm2 [54 mg</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4012,7 +6479,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -4025,22 +6492,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LIR</t>
+          <t>OBJ2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>TRT</t>
+          <t>OBJSEC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Investigational Therapy or Treatment</t>
+          <t>Study Secondary Objective; Trial Secondary Objective</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lirilumab</t>
+          <t>To document the safety profile of the xanomeline TTS.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4052,7 +6519,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CA223-002</t>
+          <t>H2Q-MC-LZZT</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -4065,27 +6532,1195 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>IPI</t>
+          <t>OBJ3</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>OBJSEC</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Study Secondary Objective; Trial Secondary Objective</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>To assess the dose-dependent improvement in behavior. Improved scores on the Revised Neuropsychiatric Inventory (NPI-X) will indicate improvement in these areas.</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>OBJ4</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>OBJSEC</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Study Secondary Objective; Trial Secondary Objective</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>To assess the dose-dependent improvements in activities of daily living. Improved scores on the Disability Assessment for Dementia (DAD) will indicate improvement in these areas (see Attachment LZZT.5).</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>4</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>OBJ5</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>OBJSEC</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Study Secondary Objective; Trial Secondary Objective</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>"To assess the dose-dependent improvements in an extended assessment of cognition that integrates attention/concentration tasks. The Alzheimer's Disease Assessment Scale-14 item Cognitive Subscale, hereafter referred to as ADAS-Cog (14), will be used for this assessment (see Attachment LZZT.2).",</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>OBJ6</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>OBJSEC</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Study Secondary Objective; Trial Secondary Objective</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>To assess the treatment response as a function of Apo E genotype.</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>OBJ1</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>OUTMSPRI</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Primary Outcome Measure</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>"Alzheimer's Disease Assessment Scale - Cognitive Subscale, total of 11 items [ADAS-Cog (11)</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>OUTMSSEC</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Secondary Outcome Measure</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>[{'OBJ2': ['&lt;p&gt;Adverse events&lt;/p&gt;', '&lt;p&gt;Vital signs (weight, standing and supine blood pressure, heart rate)&lt;/p&gt;', '&lt;p&gt;Laboratory evaluations (Change from Baseline)&lt;/p&gt;']}, {'OBJ3': ["&lt;p&gt;Alzheimer's Disease Assessment Scale - Cognitive Subscale, total of 11 items [ADAS-Cog (11)] at Weeks 8 and 16&lt;/p&gt;", '&lt;p&gt;Video-referenced Clinician s Interview-based Impression of Change (CIBIC+) at Weeks 8 and 16&lt;/p&gt;', '&lt;p&gt;Mean Revised Neuropsychiatric Inventory (NPI-X) from Week 4 to Week 24&lt;/p&gt;']}, {'OBJ4': '&lt;p&gt;*** To be determined from protocol ***&lt;/p&gt;'}, {'OBJ5': '&lt;p&gt;*** To be determined from protocol ***&lt;/p&gt;'}, {'OBJ6': '&lt;p&gt;*** To be determined from protocol ***&lt;/p&gt;'}]</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PLANSUB</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Anticipated Enrollment; Planned Enrollment; Planned Number of Subjects; Target Enrollment</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>300.0</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>XINONILINE50</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PTRTDUR</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Planned Treatment Duration</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>P24W</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>XINONILINE50</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PTRTDUR</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Planned Treatment Duration</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>P24W</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>RANDOM</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Trial is Randomized</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>XINONILINE50</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>ROUTE</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Route of Administration</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>C38288</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>http://www.cdisc.org</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>XINONILINE50</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>ROUTE</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Route of Administration</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>ORAL</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>C38288</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>//www.cdisc.org</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>SEXPOP</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Sex of Participants</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>['Female', 'Male']</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>SPONSOR</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Clinical Study Sponsor; Sponsor; Study Sponsor</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Eli Lilly</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>STYPE</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Study Type; Study Type Classification</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Interventional Study</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>C98388</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>//www.cdisc.org</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>TBLIND</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Study Blinding Design; Study Blinding Schema; Study Masking Design; Trial Blinding Design; Trial Blinding Schema; Trial Masking Design</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Double Blind Study</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>C15228</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>//www.cdisc.org</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>THERAREA</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Therapeutic Area</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>"Mild to Moderate Alzheimer's Disease", "Alzheimer's disease"</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>MILD_MOD_ALZ', '26929004</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>SPONSOR', 'SNOMED</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>12', '2025-02-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Code_152</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>TINDTP</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Trial Intent Type</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Treatment Study</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>C49656</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>http://www.cdisc.org</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Code_152_a</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>TINDTP</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Trial Intent Type</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cure Study</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>C49654</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>http://www.cdisc.org</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>TITLE</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Official Study Title; Study Title; Trial Title</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Safety and Efficacy of the Xanomeline Transdermal Therapeutic System (TTS) in Patients with Mild to Moderate Alzheimer's Disease</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>XINONILINE50</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>TRT</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Investigational Therapy or Treatment</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Ipilimumab</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> </t>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Xinomiline</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>XINONILINE25</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>TRT</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Investigational Therapy or Treatment</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Xinomiline</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>3</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>PLACEBO</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>TRT</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Investigational Therapy or Treatment</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>placebo</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Code_153</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>TTYPE</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Trial Scope; Trial Type</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Efficacy Study</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>C49666</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>http://www.cdisc.org</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Code_154</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>TTYPE</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Trial Scope; Trial Type</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Safety Study</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>C49667</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>http://www.cdisc.org</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>H2Q-MC-LZZT</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>TS</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>3</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Code_155</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>TTYPE</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Trial Scope; Trial Type</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Pharmacokinetic Study</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> </t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>C49663</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>http://www.cdisc.org</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>2025-09-26</t>
         </is>
       </c>
     </row>
@@ -4204,6 +7839,11 @@
       </c>
       <c r="G2" s="18" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
@@ -4248,7 +7888,7 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>P18Y</t>
+          <t>P50Y</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -4297,7 +7937,7 @@
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>P120Y</t>
+          <t>P100Y</t>
         </is>
       </c>
       <c r="H4" s="16" t="inlineStr">
@@ -4504,7 +8144,12 @@
           <t>Contact Name</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>{'INV01': 'Mr. X'}</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -4556,7 +8201,12 @@
           <t>Contact Role</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>{'INV01': 'Investigator'}</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -4610,7 +8260,7 @@
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>{'LIR': 'P', 'IPI': 'P'}</t>
+          <t>{'XINONILINE50': 'P1D', 'XINONILINE25': 'P1D', 'PLACEBO': 'P1D'}</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -4763,6 +8413,11 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
+          <t>{'XINONILINE50': [54.0, 81.0], 'XINONILINE25': 54.0, 'PLACEBO': 0}</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
@@ -4867,22 +8522,27 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
+          <t>{'XINONILINE50': ['QD', 'QD'], 'XINONILINE25': 'QD', 'PLACEBO': 'QD'}</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>{'StudyIntervention_1': ['C25473', 'C25473'], 'StudyIntervention_2': 'C25473', 'StudyIntervention_3': 'C25473'}</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>{'StudyIntervention_1': ['http://www.cdisc.org', 'http://www.cdisc.org'], 'StudyIntervention_2': 'http://www.cdisc.org', 'StudyIntervention_3': 'http://www.cdisc.org'}</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>{'StudyIntervention_1': ['2025-09-26', '2025-09-26'], 'StudyIntervention_2': '2025-09-26', 'StudyIntervention_3': '2025-09-26'}</t>
         </is>
       </c>
     </row>
@@ -4919,22 +8579,27 @@
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
+          <t>{'XINONILINE50': ['Milligram', 'Milligram'], 'XINONILINE25': 'Milligram', 'PLACEBO': 'Milligram'}</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>{'StudyIntervention_1': ['C28253', 'C28253'], 'StudyIntervention_2': 'C28253', 'StudyIntervention_3': 'C28253'}</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>{'StudyIntervention_1': ['http://www.cdisc.org', 'http://www.cdisc.org'], 'StudyIntervention_2': 'http://www.cdisc.org', 'StudyIntervention_3': 'http://www.cdisc.org'}</t>
         </is>
       </c>
       <c r="K16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>{'StudyIntervention_1': ['2025-09-26', '2025-09-26'], 'StudyIntervention_2': '2025-09-26', 'StudyIntervention_3': '2025-09-26'}</t>
         </is>
       </c>
     </row>
@@ -4963,6 +8628,11 @@
       </c>
       <c r="G17" s="19" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
@@ -5055,6 +8725,11 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
@@ -5099,7 +8774,7 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>{'Indication_1': 'Non-Small Cell Lung Cancer (NSCLC)', 'Indication_2': 'Castrate Resistant Prostate Cancer (CRPC)', 'Indication_3': 'Melanoma (MEL)'}</t>
+          <t>{'Indication_1': "Alzheimer's disease", 'Indication_2': "Alzheimer's disease"}</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -5148,7 +8823,7 @@
       </c>
       <c r="G21" s="20" t="inlineStr">
         <is>
-          <t>SINGLE GROUP</t>
+          <t>Parallel Study</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -5158,7 +8833,7 @@
       </c>
       <c r="I21" s="20" t="inlineStr">
         <is>
-          <t>C82640</t>
+          <t>C82639</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -5205,7 +8880,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>{'LIR': 'DRUG', 'IPI': 'DRUG'}</t>
+          <t>{'XINONILINE50': 'DRUG', 'XINONILINE25': 'DRUG', 'PLACEBO': 'DRUG'}</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -5215,21 +8890,21 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>{'StudyIntervention_1': 'C1909', 'StudyIntervention_2': 'C1909'}</t>
+          <t>{'StudyIntervention_1': 'C1909', 'StudyIntervention_2': 'C1909', 'StudyIntervention_3': 'C1909'}</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>{'StudyIntervention_1': 'http://www.cdisc.org', 'StudyIntervention_2': 'http://www.cdisc.org'}</t>
+          <t>{'StudyIntervention_1': 'http://www.cdisc.org', 'StudyIntervention_2': 'http://www.cdisc.org', 'StudyIntervention_3': 'http://www.cdisc.org'}</t>
         </is>
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>{'StudyIntervention_1': '2025-09-26', 'StudyIntervention_2': '2025-09-26'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="87" customHeight="1">
+          <t>{'StudyIntervention_1': '2025-09-26', 'StudyIntervention_2': '2025-09-26', 'StudyIntervention_3': '2025-09-26'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
       <c r="A23" s="16" t="inlineStr">
         <is>
           <t>Trial Length</t>
@@ -5301,7 +8976,7 @@
           <t>Multiple Site Eu Site Trial Indicator</t>
         </is>
       </c>
-      <c r="G24" s="18" t="inlineStr">
+      <c r="G24" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve"> </t>
         </is>
@@ -5322,7 +8997,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="29" customHeight="1">
       <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Planned Number of Arms</t>
@@ -5347,7 +9022,7 @@
       </c>
       <c r="G25" s="20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -5396,7 +9071,7 @@
       </c>
       <c r="G26" s="20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -5549,7 +9224,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>{'OBJ1': '&lt;p&gt;Primary objective texts not available from ClinicalTrials.gov.&lt;/p&gt;'}</t>
+          <t>{'OBJ1': '&lt;p&gt;To determine if there is a statistically significant relationship (overall Type 1 erroralpha=0.05) between the change in both the ADAS-Cog (11) and CIBIC+ scores, and drug dose (0, 50 cm2 [54 mg], and 75 cm2 [81 mg]).&lt;/p&gt;'}</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -5606,7 +9281,7 @@
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>{'OBJ2': '&lt;p&gt;Secondary objective texts not available from ClinicalTrials.gov.&lt;/p&gt;'}</t>
+          <t>{'OBJ2': '&lt;p&gt;To document the safety profile of the xanomeline TTS.&lt;/p&gt;', 'OBJ3': '&lt;p&gt;To assess the dose-dependent improvement in behavior. Improved scores on the Revised Neuropsychiatric Inventory (NPI-X) will indicate improvement in these areas.&lt;/p&gt;', 'OBJ4': '&lt;p&gt;To assess the dose-dependent improvements in activities of daily living. Improved scores on the Disability Assessment for Dementia (DAD) will indicate improvement in these areas (see Attachment LZZT.5).&lt;/p&gt;', 'OBJ5': "&lt;p&gt;To assess the dose-dependent improvements in an extended assessment of cognition that integrates attention/concentration tasks. The Alzheimer's Disease Assessment Scale-14 item Cognitive Subscale, hereafter referred to as ADAS-Cog (14), will be used for this assessment (see Attachment LZZT.2).&lt;/p&gt;", 'OBJ6': '&lt;p&gt;To assess the treatment response as a function of Apo E genotype.&lt;/p&gt;'}</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -5891,7 +9566,7 @@
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>{'OBJ1': '&lt;p&gt;Safety as measured by the rate of adverse events, and serious adverse events [Time Frame: Approximately 510 days]&lt;/p&gt;'}</t>
+          <t>{'OBJ1': ["&lt;p&gt;Alzheimer's Disease Assessment Scale - Cognitive Subscale, total of 11 items [ADAS-Cog (11)] at Week 24&lt;/p&gt;", '&lt;p&gt;Video-referenced Clinician s Interview-based Impression of Change (CIBIC+) at Week 24&lt;/p&gt;']}</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -5948,7 +9623,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>{'OBJ2': ['&lt;p&gt;Efficacy as measured by tumor assessment [Time Frame: Assessed from the start of treatment (ay 1) to the end of treatment (week 60) and for 90 days in follow-up]&lt;/p&gt;', '&lt;p&gt;The maximum observed serum concentration (Cmax) of BMS-986015 and Ipilimumab&lt;/p&gt;', '&lt;p&gt;The time of maximum observed serum concentration (Tmax) of BMS-986015 and Ipilimumab&lt;/p&gt;', '&lt;p&gt;Area under the serum concentration-time curve in one dosing interval [AUC(TAU)] of BMS-986015 and Ipilimumab&lt;/p&gt;', '&lt;p&gt;Area under the serum concentration-time curve from time zero extrapolated to infinite time [AUC(INF)] of BMS-986015 and Ipilimumab&lt;/p&gt;', '&lt;p&gt;Apparent total body clearance (CL) of BMS-986015 and Ipilimumab&lt;/p&gt;', '&lt;p&gt;Apparent total body clearance (CL) of BMS-986015 and Ipilimumab&lt;/p&gt;', '&lt;p&gt;Apparent volume of distribution at steady state (Vss) of BMS-986015 and Ipilimumab&lt;/p&gt;', '&lt;p&gt;Serum half-life (T-HALF) of BMS-986015 and Ipilimumab&lt;/p&gt;', '&lt;p&gt;Trough observed serum concentration (Cmin) of BMS-986015 and Ipilimumab&lt;/p&gt;', '&lt;p&gt;Immunogenicity as measured by the incidence of Ipilimumab and anti-Killer cell immunoglobulin-like receptor (KIR) (BMS-986015) anti-drug antibodies (ADA)&lt;/p&gt;']}</t>
+          <t>[{'OBJ2': ['&lt;p&gt;Adverse events&lt;/p&gt;', '&lt;p&gt;Vital signs (weight, standing and supine blood pressure, heart rate)&lt;/p&gt;', '&lt;p&gt;Laboratory evaluations (Change from Baseline)&lt;/p&gt;']}, {'OBJ3': ["&lt;p&gt;Alzheimer's Disease Assessment Scale - Cognitive Subscale, total of 11 items [ADAS-Cog (11)] at Weeks 8 and 16&lt;/p&gt;", '&lt;p&gt;Video-referenced Clinician s Interview-based Impression of Change (CIBIC+) at Weeks 8 and 16&lt;/p&gt;', '&lt;p&gt;Mean Revised Neuropsychiatric Inventory (NPI-X) from Week 4 to Week 24&lt;/p&gt;']}, {'OBJ4': '&lt;p&gt;*** To be determined from protocol ***&lt;/p&gt;'}, {'OBJ5': '&lt;p&gt;*** To be determined from protocol ***&lt;/p&gt;'}, {'OBJ6': '&lt;p&gt;*** To be determined from protocol ***&lt;/p&gt;'}]</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -6089,7 +9764,7 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>150.0</t>
+          <t>300.0</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6142,12 +9817,12 @@
       </c>
       <c r="G41" s="20" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>{'XINONILINE50': ['P24W', 'P24W'], 'XINONILINE25': 'P24W', 'PLACEBO': 'P24W'}</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>NI</t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -6191,6 +9866,11 @@
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
@@ -6339,22 +10019,27 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
+          <t>{'XINONILINE50': ['ORAL', 'ORAL'], 'XINONILINE25': 'ORAL', 'PLACEBO': 'ORAL'}</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>{'StudyIntervention_1': ['C38288', 'C38288'], 'StudyIntervention_2': 'C38288', 'StudyIntervention_3': 'C38288'}</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>{'StudyIntervention_1': ['http://www.cdisc.org', 'http://www.cdisc.org'], 'StudyIntervention_2': 'http://www.cdisc.org', 'StudyIntervention_3': 'http://www.cdisc.org'}</t>
         </is>
       </c>
       <c r="K45" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>{'StudyIntervention_1': ['2025-09-26', '2025-09-26'], 'StudyIntervention_2': '2025-09-26', 'StudyIntervention_3': '2025-09-26'}</t>
         </is>
       </c>
     </row>
@@ -6484,7 +10169,7 @@
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -6674,7 +10359,7 @@
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>OPEN LABEL</t>
+          <t>Double Blind Study</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6684,7 +10369,7 @@
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>C49659</t>
+          <t>C15228</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
@@ -6767,7 +10452,7 @@
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>Oncology</t>
+          <t>"Mild to Moderate Alzheimer's Disease", "Alzheimer's disease"</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -6777,17 +10462,17 @@
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>LP32910-9</t>
+          <t>MILD_MOD_ALZ', '26929004</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>LOINC</t>
+          <t>SPONSOR', 'SNOMED</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>12', '2025-02-01</t>
         </is>
       </c>
     </row>
@@ -6820,7 +10505,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>{'Code_152': 'Treatment Study'}</t>
+          <t>{'Code_152': 'Treatment Study', 'Code_152_a': 'Cure Study'}</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6830,17 +10515,17 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>{'Code_152': 'C49656'}</t>
+          <t>{'Code_152': 'C49656', 'Code_152_a': 'C49654'}</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>{'Code_152': 'http://www.cdisc.org'}</t>
+          <t>{'Code_152': 'http://www.cdisc.org', 'Code_152_a': 'http://www.cdisc.org'}</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
         <is>
-          <t>{'Code_152': '2025-09-26'}</t>
+          <t>{'Code_152': '2025-09-26', 'Code_152_a': '2025-09-26'}</t>
         </is>
       </c>
     </row>
@@ -6869,7 +10554,7 @@
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>A Phase 1 Study of BMS-986015, an Anti-KIR Monoclonal Antibody, Administered With Ipilimumab, an Anti-CTLA4 Monoclonal Antibody, in Subjects With Select Advanced Solid Tumors</t>
+          <t>Safety and Efficacy of the Xanomeline Transdermal Therapeutic System (TTS) in Patients with Mild to Moderate Alzheimer's Disease</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6975,7 +10660,7 @@
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>{'LIR': 'Lirilumab', 'IPI': 'Ipilimumab'}</t>
+          <t>{'XINONILINE50': 'Xinomiline', 'XINONILINE25': 'Xinomiline', 'PLACEBO': 'placebo'}</t>
         </is>
       </c>
       <c r="H58" s="16" t="inlineStr">
@@ -7024,22 +10709,27 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
+          <t>{'Code_153': 'Efficacy Study', 'Code_154': 'Safety Study', 'Code_155': 'Pharmacokinetic Study'}</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
           <t xml:space="preserve"> </t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>{'Code_153': 'C49666', 'Code_154': 'C49667', 'Code_155': 'C49663'}</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>{'Code_153': 'http://www.cdisc.org', 'Code_154': 'http://www.cdisc.org', 'Code_155': 'http://www.cdisc.org'}</t>
         </is>
       </c>
       <c r="K59" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve"> </t>
+          <t>{'Code_153': '2025-09-26', 'Code_154': '2025-09-26', 'Code_155': '2025-09-26'}</t>
         </is>
       </c>
     </row>
